--- a/downloads/10.5281_zenodo.19682162/cb_parc_alignedstudies_teenagers.xlsx
+++ b/downloads/10.5281_zenodo.19682162/cb_parc_alignedstudies_teenagers.xlsx
@@ -19104,7 +19104,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>20270427</v>
+        <v>20270430</v>
       </c>
     </row>
   </sheetData>
@@ -60279,8 +60279,8 @@
     <col min="15" max="15" width="15.71" hidden="0" customWidth="1"/>
     <col min="16" max="16" width="8.71" hidden="0" customWidth="1"/>
     <col min="17" max="17" width="8.71" hidden="0" customWidth="1"/>
-    <col min="18" max="18" width="209.71" hidden="0" customWidth="1"/>
-    <col min="19" max="19" width="172.71" hidden="0" customWidth="1"/>
+    <col min="18" max="18" width="207.71" hidden="0" customWidth="1"/>
+    <col min="19" max="19" width="169.71" hidden="0" customWidth="1"/>
     <col min="20" max="20" width="17.71" hidden="0" customWidth="1"/>
     <col min="21" max="21" width="6.71" hidden="0" customWidth="1"/>
   </cols>
@@ -65009,8 +65009,8 @@
     <col min="15" max="15" width="15.71" hidden="0" customWidth="1"/>
     <col min="16" max="16" width="8.71" hidden="0" customWidth="1"/>
     <col min="17" max="17" width="8.71" hidden="0" customWidth="1"/>
-    <col min="18" max="18" width="209.71" hidden="0" customWidth="1"/>
-    <col min="19" max="19" width="172.71" hidden="0" customWidth="1"/>
+    <col min="18" max="18" width="207.71" hidden="0" customWidth="1"/>
+    <col min="19" max="19" width="169.71" hidden="0" customWidth="1"/>
     <col min="20" max="20" width="17.71" hidden="0" customWidth="1"/>
     <col min="21" max="21" width="6.71" hidden="0" customWidth="1"/>
   </cols>
@@ -71092,7 +71092,7 @@
     <col min="4" max="4" width="50.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="90.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="14.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="211.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="210.71" hidden="0" customWidth="1"/>
     <col min="8" max="8" width="11.71" hidden="0" customWidth="1"/>
     <col min="9" max="9" width="6.71" hidden="0" customWidth="1"/>
     <col min="10" max="10" width="15.71" hidden="0" customWidth="1"/>
@@ -73010,7 +73010,7 @@
     <col min="1" max="1" width="7.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="6.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="14.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="125.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="124.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="137.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="29.71" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="14.71" hidden="0" customWidth="1"/>
@@ -74382,7 +74382,7 @@
     <col min="12" max="12" width="17.71" hidden="0" customWidth="1"/>
     <col min="13" max="13" width="13.71" hidden="0" customWidth="1"/>
     <col min="14" max="14" width="18.71" hidden="0" customWidth="1"/>
-    <col min="15" max="15" width="83.71" hidden="0" customWidth="1"/>
+    <col min="15" max="15" width="82.71" hidden="0" customWidth="1"/>
     <col min="16" max="16" width="7.71" hidden="0" customWidth="1"/>
     <col min="17" max="17" width="6.71" hidden="0" customWidth="1"/>
   </cols>

--- a/downloads/10.5281_zenodo.19682162/cb_parc_alignedstudies_teenagers.xlsx
+++ b/downloads/10.5281_zenodo.19682162/cb_parc_alignedstudies_teenagers.xlsx
@@ -16913,21 +16913,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="7.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="14.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="6.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="12.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="116.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="11.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="15.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="8.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="8.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="60.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="250.71" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="17.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="6.71" hidden="0" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
@@ -17103,25 +17088,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="7.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="6.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="13.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="11.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="102.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="5.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="250.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="15.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="8.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="8.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="250.71" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="17.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="13.71" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="18.71" hidden="0" customWidth="1"/>
-    <col min="15" max="15" width="250.71" hidden="0" customWidth="1"/>
-    <col min="16" max="16" width="7.71" hidden="0" customWidth="1"/>
-    <col min="17" max="17" width="6.71" hidden="0" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
@@ -18321,25 +18287,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="7.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="6.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="28.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="196.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="11.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="4.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="15.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="8.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="8.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="250.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="18.71" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="69.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="7.71" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="180.71" hidden="0" customWidth="1"/>
-    <col min="15" max="15" width="17.71" hidden="0" customWidth="1"/>
-    <col min="16" max="16" width="6.71" hidden="0" customWidth="1"/>
-    <col min="17" max="17" width="6.71" hidden="0" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
@@ -19096,9 +19043,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="8.71" hidden="0" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
@@ -19123,31 +19067,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="7.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="13.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="17.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="209.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="18.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="6.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="33.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="11.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="7.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="42.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="64.71" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="250.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="149.71" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="11.71" hidden="0" customWidth="1"/>
-    <col min="15" max="15" width="250.71" hidden="0" customWidth="1"/>
-    <col min="16" max="16" width="15.71" hidden="0" customWidth="1"/>
-    <col min="17" max="17" width="8.71" hidden="0" customWidth="1"/>
-    <col min="18" max="18" width="8.71" hidden="0" customWidth="1"/>
-    <col min="19" max="19" width="18.71" hidden="0" customWidth="1"/>
-    <col min="20" max="20" width="250.71" hidden="0" customWidth="1"/>
-    <col min="21" max="21" width="250.71" hidden="0" customWidth="1"/>
-    <col min="22" max="22" width="17.71" hidden="0" customWidth="1"/>
-    <col min="23" max="23" width="6.71" hidden="0" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
@@ -60266,29 +60185,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="7.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="9.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="17.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="18.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="6.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="30.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="11.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="7.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="54.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="22.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="197.71" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="102.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="7.71" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="135.71" hidden="0" customWidth="1"/>
-    <col min="15" max="15" width="15.71" hidden="0" customWidth="1"/>
-    <col min="16" max="16" width="8.71" hidden="0" customWidth="1"/>
-    <col min="17" max="17" width="8.71" hidden="0" customWidth="1"/>
-    <col min="18" max="18" width="207.71" hidden="0" customWidth="1"/>
-    <col min="19" max="19" width="169.71" hidden="0" customWidth="1"/>
-    <col min="20" max="20" width="17.71" hidden="0" customWidth="1"/>
-    <col min="21" max="21" width="6.71" hidden="0" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
@@ -64996,29 +64892,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="7.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="9.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="17.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="18.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="6.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="30.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="11.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="7.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="54.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="34.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="235.71" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="102.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="7.71" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="150.71" hidden="0" customWidth="1"/>
-    <col min="15" max="15" width="15.71" hidden="0" customWidth="1"/>
-    <col min="16" max="16" width="8.71" hidden="0" customWidth="1"/>
-    <col min="17" max="17" width="8.71" hidden="0" customWidth="1"/>
-    <col min="18" max="18" width="207.71" hidden="0" customWidth="1"/>
-    <col min="19" max="19" width="169.71" hidden="0" customWidth="1"/>
-    <col min="20" max="20" width="17.71" hidden="0" customWidth="1"/>
-    <col min="21" max="21" width="6.71" hidden="0" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
@@ -70535,23 +70408,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="7.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="14.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="6.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="10.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="42.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="11.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="8.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="8.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="18.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="15.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="5.71" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="148.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="7.71" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="17.71" hidden="0" customWidth="1"/>
-    <col min="15" max="15" width="6.71" hidden="0" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
@@ -71090,23 +70946,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="7.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="6.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="14.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="50.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="90.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="14.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="210.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="11.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="6.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="15.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="8.71" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="8.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="98.71" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="59.71" hidden="0" customWidth="1"/>
-    <col min="15" max="15" width="17.71" hidden="0" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
@@ -73011,25 +72850,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="7.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="6.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="14.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="124.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="137.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="29.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="14.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="250.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="109.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="11.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="6.71" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="15.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="8.71" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="8.71" hidden="0" customWidth="1"/>
-    <col min="15" max="15" width="51.71" hidden="0" customWidth="1"/>
-    <col min="16" max="16" width="143.71" hidden="0" customWidth="1"/>
-    <col min="17" max="17" width="17.71" hidden="0" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
@@ -74372,25 +74192,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="7.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="6.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="13.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="11.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="94.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="5.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="250.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="15.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="8.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="8.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="250.71" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="17.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="13.71" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="18.71" hidden="0" customWidth="1"/>
-    <col min="15" max="15" width="82.71" hidden="0" customWidth="1"/>
-    <col min="16" max="16" width="7.71" hidden="0" customWidth="1"/>
-    <col min="17" max="17" width="6.71" hidden="0" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
@@ -81480,25 +81281,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="7.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="6.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="16.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="11.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="79.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="7.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="250.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="15.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="8.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="8.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="250.71" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="17.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="13.71" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="18.71" hidden="0" customWidth="1"/>
-    <col min="15" max="15" width="250.71" hidden="0" customWidth="1"/>
-    <col min="16" max="16" width="7.71" hidden="0" customWidth="1"/>
-    <col min="17" max="17" width="6.71" hidden="0" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
